--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488016_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488016_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5872</v>
+        <v>11.1766</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4039</v>
+        <v>9.077500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1834</v>
+        <v>2.0991</v>
       </c>
       <c r="G2" t="n">
         <v>7.0708</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>0.12</v>
+        <v>0.7094</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2972</v>
+        <v>0.3765</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4172</v>
+        <v>0.3329</v>
       </c>
       <c r="V2" t="n">
         <v>1.8107</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. HUNT</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6069</v>
+        <v>4.6775</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0625</v>
+        <v>1.9516</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6693</v>
+        <v>2.7259</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7693</v>
+        <v>5.4002</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0837</v>
+        <v>2.4843</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6857</v>
+        <v>2.9159</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4482</v>
+        <v>4.3659</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8129</v>
+        <v>1.8633</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2611</v>
+        <v>2.5027</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3212</v>
+        <v>1.0342</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8966</v>
+        <v>0.621</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4246</v>
+        <v>0.4132</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1805</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3787</v>
+        <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.213</v>
+        <v>0.1386</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1121</v>
+        <v>-0.2339</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8991</v>
+        <v>0.3725</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8701</v>
+        <v>-0.2666</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0704</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>B. HUNT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4362</v>
+        <v>4.6171</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9911</v>
+        <v>0.5093</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4451</v>
+        <v>4.1078</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4002</v>
+        <v>1.7693</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4843</v>
+        <v>0.0837</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9159</v>
+        <v>1.6857</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3659</v>
+        <v>0.4482</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8633</v>
+        <v>-0.8129</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5027</v>
+        <v>1.2611</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0342</v>
+        <v>1.3212</v>
       </c>
       <c r="N4" t="n">
-        <v>0.621</v>
+        <v>0.8966</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4132</v>
+        <v>0.4246</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5947</v>
+        <v>2.1805</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5858</v>
+        <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1027</v>
+        <v>-0.2029</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1944</v>
+        <v>-0.5404</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0917</v>
+        <v>0.3375</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2666</v>
+        <v>0.8701</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2666</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>A. VAZQUEZ ASTILLEROS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0956</v>
+        <v>1.1367</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.3072</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1588</v>
+        <v>1.4438</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5945</v>
+        <v>-0.577</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7347</v>
+        <v>-0.2328</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1403</v>
+        <v>-0.3442</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1984</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.405</v>
+        <v>0.0271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7271</v>
+        <v>-0.2255</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0834</v>
+        <v>-0.3786</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3298</v>
+        <v>-0.2599</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>-0.1187</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9764</v>
+        <v>-0.4845</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2886</v>
+        <v>-0.3247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6878</v>
+        <v>-0.1598</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.674</v>
+        <v>1.2071</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.674</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ ASTILLEROS</t>
+          <t>P. FERNANDEZ ANTUNEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5089</v>
+        <v>1.1255</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1034</v>
+        <v>-0.4939</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6123</v>
+        <v>1.6194</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.577</v>
+        <v>0.2041</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2328</v>
+        <v>-0.1575</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3442</v>
+        <v>0.3616</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1984</v>
+        <v>0.5788</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0271</v>
+        <v>0.3701</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2255</v>
+        <v>0.2087</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3786</v>
+        <v>-0.3747</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2599</v>
+        <v>-0.5276</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1187</v>
+        <v>0.1529</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9822</v>
+        <v>2.3787</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1123</v>
+        <v>-0.2679</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.121</v>
+        <v>0.1167</v>
       </c>
       <c r="U7" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.3846</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ ANTUNEZ</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3491</v>
+        <v>0.8689</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4107</v>
+        <v>-1.1214</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7598</v>
+        <v>1.9903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2041</v>
+        <v>-0.5945</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1575</v>
+        <v>-1.7347</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3616</v>
+        <v>1.1403</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5788</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3701</v>
+        <v>-1.405</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2087</v>
+        <v>0.7271</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3747</v>
+        <v>0.0834</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5276</v>
+        <v>-0.3298</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1529</v>
+        <v>0.4132</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3787</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0444</v>
+        <v>0.7498</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8001</v>
+        <v>0.2305</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2442</v>
+        <v>0.5193</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0036</v>
+        <v>0.1016</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4473</v>
+        <v>0.2436</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4509</v>
+        <v>-0.1421</v>
       </c>
       <c r="G10" t="n">
         <v>0.2515</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8044</v>
+        <v>0.9095</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8701</v>
+        <v>0.6664</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.2431</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2666</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GUTIERREZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9727</v>
+        <v>-0.1235</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1625</v>
+        <v>-1.7244</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1898</v>
+        <v>1.601</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9249</v>
+        <v>-0.6856</v>
       </c>
       <c r="H12" t="n">
-        <v>0.34</v>
+        <v>-2.4075</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.265</v>
+        <v>1.7219</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.291</v>
+        <v>-1.2524</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0605</v>
+        <v>-1.3444</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.3516</v>
+        <v>0.092</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3661</v>
+        <v>0.5669</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2795</v>
+        <v>-1.0631</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0866</v>
+        <v>1.6299</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3964</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5558</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1286</v>
+        <v>0.4507</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4272</v>
+        <v>0.2412</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>S. MARTINEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.0602</v>
+        <v>-1.166</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2962</v>
+        <v>-3.4681</v>
       </c>
       <c r="F13" t="n">
-        <v>1.236</v>
+        <v>2.3021</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6856</v>
+        <v>-1.9249</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4075</v>
+        <v>0.34</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7219</v>
+        <v>-2.265</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2524</v>
+        <v>-3.291</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3444</v>
+        <v>0.0605</v>
       </c>
       <c r="L13" t="n">
-        <v>0.092</v>
+        <v>-3.3516</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5669</v>
+        <v>1.3661</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0631</v>
+        <v>0.2795</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6299</v>
+        <v>1.0866</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3964</v>
+        <v>0.3964</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2448</v>
+        <v>0.3625</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.121</v>
+        <v>-0.177</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1238</v>
+        <v>0.5395</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.7977</v>
+        <v>-3.3528</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4209</v>
+        <v>-2.0321</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3768</v>
+        <v>-1.3207</v>
       </c>
       <c r="G14" t="n">
         <v>-1.1073</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9993</v>
+        <v>0.4442</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2483</v>
+        <v>0.6371</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.249</v>
+        <v>-0.1929</v>
       </c>
       <c r="V14" t="n">
         <v>-3.2843</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>22.1661</v>
+        <v>22.47800000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>5.774799999999999</v>
+        <v>6.0868</v>
       </c>
       <c r="F15" t="n">
-        <v>16.3912</v>
+        <v>16.391</v>
       </c>
       <c r="G15" t="n">
         <v>14.9963</v>
@@ -1600,13 +1600,13 @@
         <v>8.6417</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4669999999999998</v>
+        <v>-0.4670000000000002</v>
       </c>
       <c r="L15" t="n">
-        <v>9.1088</v>
+        <v>9.108800000000002</v>
       </c>
       <c r="M15" t="n">
-        <v>6.354800000000001</v>
+        <v>6.354800000000002</v>
       </c>
       <c r="N15" t="n">
         <v>-1.8807</v>
@@ -1624,13 +1624,13 @@
         <v>14.8667</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7167</v>
+        <v>3.0287</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5153999999999999</v>
+        <v>0.8274999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2014</v>
+        <v>2.2011</v>
       </c>
       <c r="V15" t="n">
         <v>-2.4846</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3464</v>
+        <v>1.2833</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7844</v>
+        <v>1.562</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.438</v>
+        <v>-0.2787</v>
       </c>
       <c r="G16" t="n">
         <v>1.0116</v>
@@ -1702,13 +1702,13 @@
         <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9383</v>
+        <v>-0.1248</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1566</v>
+        <v>-0.0658</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2183</v>
+        <v>-0.0589</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7789</v>
+        <v>1.0727</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3877</v>
+        <v>-0.2858</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1665</v>
+        <v>1.3585</v>
       </c>
       <c r="G17" t="n">
         <v>0.8773</v>
@@ -1780,13 +1780,13 @@
         <v>0.1982</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2966</v>
+        <v>-0.0028</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3744</v>
+        <v>-0.2725</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.2698</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1128</v>
+        <v>0.1389</v>
       </c>
       <c r="E19" t="n">
-        <v>0.032</v>
+        <v>0.2357</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0808</v>
+        <v>-0.0968</v>
       </c>
       <c r="G19" t="n">
         <v>-0.645</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1895</v>
+        <v>-0.1634</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4844</v>
+        <v>-0.2806</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2948</v>
+        <v>0.1172</v>
       </c>
       <c r="V19" t="n">
         <v>1.7403</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9144</v>
+        <v>-0.8687</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9911</v>
+        <v>-0.8892</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0767</v>
+        <v>0.0205</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0752</v>
@@ -2014,13 +2014,13 @@
         <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0374</v>
+        <v>0.0083</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2745</v>
+        <v>0.2184</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0675</v>
+        <v>-0.8814</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4521</v>
+        <v>-0.3502</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.5311</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3579</v>
@@ -2092,13 +2092,13 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2448</v>
+        <v>-0.0587</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.301</v>
+        <v>-0.1991</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0562</v>
+        <v>0.1404</v>
       </c>
       <c r="V21" t="n">
         <v>0.9405</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4088</v>
+        <v>-1.9289</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5158</v>
+        <v>-0.3121</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.893</v>
+        <v>-1.6168</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9901</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6259</v>
+        <v>-0.1459</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0476</v>
+        <v>0.1562</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5783</v>
+        <v>-0.3021</v>
       </c>
       <c r="V22" t="n">
         <v>1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4761</v>
+        <v>-2.5988</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1935</v>
+        <v>-2.0916</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2826</v>
+        <v>-0.5072</v>
       </c>
       <c r="G23" t="n">
         <v>-2.106</v>
@@ -2248,13 +2248,13 @@
         <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2246</v>
+        <v>0.1019</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4257</v>
+        <v>-0.3239</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6504</v>
+        <v>0.4257</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7152</v>
+        <v>-3.0537</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0276</v>
+        <v>-1.722</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6876</v>
+        <v>-1.3317</v>
       </c>
       <c r="G24" t="n">
         <v>0.449</v>
@@ -2326,13 +2326,13 @@
         <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7588</v>
+        <v>-0.0973</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.433</v>
+        <v>-0.1274</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3258</v>
+        <v>0.0301</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4142</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.987</v>
+        <v>-4.1241</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3556</v>
+        <v>-3.6612</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6314</v>
+        <v>-0.4629</v>
       </c>
       <c r="G25" t="n">
         <v>-2.3305</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1344</v>
+        <v>-0.0028</v>
       </c>
       <c r="T25" t="n">
-        <v>0.191</v>
+        <v>-0.1146</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0566</v>
+        <v>0.1119</v>
       </c>
       <c r="V25" t="n">
         <v>-0.7997</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5977</v>
+        <v>-4.7838</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6665</v>
+        <v>-3.7684</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9312</v>
+        <v>-1.0154</v>
       </c>
       <c r="G26" t="n">
         <v>-2.3904</v>
@@ -2482,13 +2482,13 @@
         <v>0.1982</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2251</v>
+        <v>-0.4112</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2568</v>
+        <v>-0.3587</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0318</v>
+        <v>-0.0525</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.5401</v>
+        <v>-5.366</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.9203</v>
+        <v>-5.411</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6198</v>
+        <v>0.045</v>
       </c>
       <c r="G27" t="n">
         <v>-3.7417</v>
@@ -2560,13 +2560,13 @@
         <v>1.1893</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.6357</v>
+        <v>-0.4616</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9139</v>
+        <v>-0.4045</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.7218</v>
+        <v>-0.0571</v>
       </c>
       <c r="V27" t="n">
         <v>1.8107</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-22.166</v>
+        <v>-20.8078</v>
       </c>
       <c r="E28" t="n">
         <v>-16.3911</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.775</v>
+        <v>-4.416600000000001</v>
       </c>
       <c r="G28" t="n">
         <v>-14.9962</v>
@@ -2638,13 +2638,13 @@
         <v>7.928900000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.7165</v>
+        <v>-1.3583</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.2012</v>
+        <v>-2.201</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.5153000000000001</v>
+        <v>0.8429</v>
       </c>
       <c r="V28" t="n">
         <v>2.4847</v>
